--- a/submission/셀프체크리스트_결과.xlsx
+++ b/submission/셀프체크리스트_결과.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SSAFY\Desktop\disease\kdca-rag-stage1\kdca-rag\submission\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35C8D618-EBEE-4BBE-906C-CDDEF6BE107A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD2CC033-3CBE-4FBA-B4D7-C47304EA3C9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="17475" yWindow="915" windowWidth="18720" windowHeight="15345" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="체크리스트" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="186">
   <si>
     <t>[SSAFY] AI 코어 프로젝트 2회차 — 셀프 · 상호 체크리스트</t>
   </si>
@@ -61,9 +61,6 @@
     <t>앱 작성자</t>
   </si>
   <si>
-    <t>이름</t>
-  </si>
-  <si>
     <t>점검자</t>
   </si>
   <si>
@@ -512,9 +509,6 @@
   </si>
   <si>
     <t>요구사항_대조표.md, 테스트_결과표.md</t>
-  </si>
-  <si>
-    <t>요구사항 정의서·설계문서·소스·README·대조표·테스트 결과표·셀프 체크리스트 포함 / 상호 체크리스트는 옆 교육생 점검 후 submission/에 추가해야 함</t>
   </si>
   <si>
     <t>집계</t>
@@ -603,6 +597,22 @@
   </si>
   <si>
     <t>GMS 응답 지연으로 측정 못 함 → 상호 점검 전에 다시 측정</t>
+  </si>
+  <si>
+    <t>양채연</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>요구사항 정의서·설계문서·소스·README·대조표·테스트 결과표·셀프 체크리스트 포함 / 상호 체크리스트는 옆 교육생 점검 후 submission/에 추가해야 함</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>근거와 출처를 명확히 했으며 확인되지 않는 질문에는 솔직히 모른다고 답함, RAG 전후 비교에서 정확도와 근거 제시율을 측정함.</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>답변까지 걸리는 속도를 줄이는 목적으로 첫 답변은 위키 문서 하나를 근거로 답하고, 추가 문서는 그 뒤에 모으므로 첫 답변의 근거가 얕을 수 있음. 첫 답변에도 추가 수집을 기다릴지 고르게 하면 개선할 수 있을 것으로 기대.</t>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -939,7 +949,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -993,24 +1003,29 @@
     <xf numFmtId="0" fontId="4" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
@@ -1023,13 +1038,8 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1039,9 +1049,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1371,26 +1378,26 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:9" ht="39.75" customHeight="1">
-      <c r="B2" s="35" t="s">
+      <c r="B2" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="36"/>
-      <c r="D2" s="36"/>
-      <c r="E2" s="36"/>
-      <c r="F2" s="36"/>
-      <c r="G2" s="36"/>
-      <c r="H2" s="36"/>
-      <c r="I2" s="37"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
+      <c r="G2" s="37"/>
+      <c r="H2" s="37"/>
+      <c r="I2" s="38"/>
     </row>
     <row r="3" spans="2:9" ht="24" customHeight="1">
       <c r="B3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="41" t="s">
+      <c r="C3" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="20"/>
-      <c r="E3" s="21"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="20"/>
       <c r="F3" s="27" t="s">
         <v>3</v>
       </c>
@@ -1402,887 +1409,879 @@
       <c r="B4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="41" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4" s="20"/>
-      <c r="E4" s="21"/>
+      <c r="C4" s="26" t="s">
+        <v>182</v>
+      </c>
+      <c r="D4" s="19"/>
+      <c r="E4" s="20"/>
       <c r="F4" s="30"/>
-      <c r="G4" s="23"/>
-      <c r="H4" s="23"/>
-      <c r="I4" s="31"/>
+      <c r="G4" s="31"/>
+      <c r="H4" s="31"/>
+      <c r="I4" s="32"/>
     </row>
     <row r="5" spans="2:9" ht="24" customHeight="1">
       <c r="B5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="41"/>
-      <c r="D5" s="20"/>
-      <c r="E5" s="21"/>
+        <v>5</v>
+      </c>
+      <c r="C5" s="26" t="s">
+        <v>182</v>
+      </c>
+      <c r="D5" s="19"/>
+      <c r="E5" s="20"/>
       <c r="F5" s="30"/>
-      <c r="G5" s="23"/>
-      <c r="H5" s="23"/>
-      <c r="I5" s="31"/>
+      <c r="G5" s="31"/>
+      <c r="H5" s="31"/>
+      <c r="I5" s="32"/>
     </row>
     <row r="6" spans="2:9" ht="24" customHeight="1">
       <c r="B6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="41" t="s">
+      <c r="D6" s="19"/>
+      <c r="E6" s="20"/>
+      <c r="F6" s="33"/>
+      <c r="G6" s="34"/>
+      <c r="H6" s="34"/>
+      <c r="I6" s="35"/>
+    </row>
+    <row r="7" spans="2:9" ht="18" customHeight="1">
+      <c r="B7" s="40" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="20"/>
-      <c r="E6" s="21"/>
-      <c r="F6" s="32"/>
-      <c r="G6" s="33"/>
-      <c r="H6" s="33"/>
-      <c r="I6" s="34"/>
-    </row>
-    <row r="7" spans="2:9" ht="18" customHeight="1">
-      <c r="B7" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="23"/>
-      <c r="D7" s="23"/>
-      <c r="E7" s="23"/>
-      <c r="F7" s="23"/>
-      <c r="G7" s="23"/>
-      <c r="H7" s="23"/>
-      <c r="I7" s="23"/>
+      <c r="C7" s="31"/>
+      <c r="D7" s="31"/>
+      <c r="E7" s="31"/>
+      <c r="F7" s="31"/>
+      <c r="G7" s="31"/>
+      <c r="H7" s="31"/>
+      <c r="I7" s="31"/>
     </row>
     <row r="8" spans="2:9" ht="24" customHeight="1">
       <c r="B8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="D8" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="E8" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="F8" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="G8" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="G8" s="2" t="s">
+      <c r="H8" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="H8" s="2" t="s">
+      <c r="I8" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="I8" s="2" t="s">
+    </row>
+    <row r="9" spans="2:9" ht="34.5" customHeight="1">
+      <c r="B9" s="21" t="s">
         <v>17</v>
-      </c>
-    </row>
-    <row r="9" spans="2:9" ht="34.5" customHeight="1">
-      <c r="B9" s="24" t="s">
-        <v>18</v>
       </c>
       <c r="C9" s="4">
         <v>1</v>
       </c>
       <c r="D9" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="F9" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="F9" s="3" t="s">
-        <v>21</v>
-      </c>
       <c r="G9" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H9" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="H9" s="6" t="s">
+      <c r="I9" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="I9" s="6" t="s">
-        <v>24</v>
-      </c>
     </row>
     <row r="10" spans="2:9" ht="24" customHeight="1">
-      <c r="B10" s="26"/>
+      <c r="B10" s="23"/>
       <c r="C10" s="4">
         <v>2</v>
       </c>
       <c r="D10" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E10" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="F10" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="F10" s="3" t="s">
+      <c r="G10" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H10" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="G10" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="H10" s="6" t="s">
+      <c r="I10" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="I10" s="6" t="s">
+    </row>
+    <row r="11" spans="2:9" ht="48" customHeight="1">
+      <c r="B11" s="21" t="s">
         <v>29</v>
-      </c>
-    </row>
-    <row r="11" spans="2:9" ht="48" customHeight="1">
-      <c r="B11" s="24" t="s">
-        <v>30</v>
       </c>
       <c r="C11" s="4">
         <v>3</v>
       </c>
       <c r="D11" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E11" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="E11" s="3" t="s">
+      <c r="F11" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="F11" s="3" t="s">
+      <c r="G11" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H11" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="G11" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="H11" s="6" t="s">
+      <c r="I11" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="I11" s="6" t="s">
-        <v>35</v>
-      </c>
     </row>
     <row r="12" spans="2:9" ht="34.5" customHeight="1">
-      <c r="B12" s="25"/>
+      <c r="B12" s="22"/>
       <c r="C12" s="4">
         <v>4</v>
       </c>
       <c r="D12" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E12" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="E12" s="3" t="s">
+      <c r="F12" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="F12" s="3" t="s">
+      <c r="G12" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H12" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="G12" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="H12" s="6" t="s">
+      <c r="I12" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="I12" s="6" t="s">
-        <v>40</v>
-      </c>
     </row>
     <row r="13" spans="2:9" ht="34.5" customHeight="1">
-      <c r="B13" s="26"/>
+      <c r="B13" s="23"/>
       <c r="C13" s="4">
         <v>5</v>
       </c>
       <c r="D13" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E13" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E13" s="3" t="s">
+      <c r="F13" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="F13" s="3" t="s">
+      <c r="G13" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H13" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="G13" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="H13" s="6" t="s">
+      <c r="I13" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="I13" s="6" t="s">
+    </row>
+    <row r="14" spans="2:9" ht="34.5" customHeight="1">
+      <c r="B14" s="21" t="s">
         <v>45</v>
-      </c>
-    </row>
-    <row r="14" spans="2:9" ht="34.5" customHeight="1">
-      <c r="B14" s="24" t="s">
-        <v>46</v>
       </c>
       <c r="C14" s="4">
         <v>6</v>
       </c>
       <c r="D14" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="E14" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="E14" s="3" t="s">
+      <c r="F14" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="F14" s="7" t="s">
+      <c r="G14" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H14" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="G14" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="H14" s="6" t="s">
+      <c r="I14" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="I14" s="6" t="s">
-        <v>51</v>
-      </c>
     </row>
     <row r="15" spans="2:9" ht="34.5" customHeight="1">
-      <c r="B15" s="25"/>
+      <c r="B15" s="22"/>
       <c r="C15" s="4">
         <v>7</v>
       </c>
       <c r="D15" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="E15" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="E15" s="7" t="s">
+      <c r="F15" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="F15" s="3" t="s">
+      <c r="G15" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H15" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="G15" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="H15" s="6" t="s">
+      <c r="I15" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="I15" s="6" t="s">
-        <v>56</v>
-      </c>
     </row>
     <row r="16" spans="2:9" ht="34.5" customHeight="1">
-      <c r="B16" s="25"/>
+      <c r="B16" s="22"/>
       <c r="C16" s="4">
         <v>8</v>
       </c>
       <c r="D16" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E16" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="E16" s="3" t="s">
+      <c r="F16" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="F16" s="3" t="s">
+      <c r="G16" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H16" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="G16" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="H16" s="6" t="s">
+      <c r="I16" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="I16" s="6" t="s">
-        <v>61</v>
-      </c>
     </row>
     <row r="17" spans="2:9" ht="48" customHeight="1">
-      <c r="B17" s="26"/>
+      <c r="B17" s="23"/>
       <c r="C17" s="4">
         <v>9</v>
       </c>
       <c r="D17" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="E17" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="E17" s="3" t="s">
+      <c r="F17" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F17" s="3" t="s">
+      <c r="G17" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H17" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="G17" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="H17" s="6" t="s">
+      <c r="I17" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="I17" s="6" t="s">
+    </row>
+    <row r="18" spans="2:9" ht="24" customHeight="1">
+      <c r="B18" s="21" t="s">
         <v>66</v>
-      </c>
-    </row>
-    <row r="18" spans="2:9" ht="24" customHeight="1">
-      <c r="B18" s="24" t="s">
-        <v>67</v>
       </c>
       <c r="C18" s="4">
         <v>10</v>
       </c>
       <c r="D18" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="E18" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="E18" s="3" t="s">
+      <c r="F18" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="F18" s="3" t="s">
+      <c r="G18" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H18" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="G18" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="H18" s="6" t="s">
+      <c r="I18" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="I18" s="6" t="s">
-        <v>72</v>
-      </c>
     </row>
     <row r="19" spans="2:9" ht="34.5" customHeight="1">
-      <c r="B19" s="25"/>
+      <c r="B19" s="22"/>
       <c r="C19" s="4">
         <v>11</v>
       </c>
       <c r="D19" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="E19" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="E19" s="3" t="s">
+      <c r="F19" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="F19" s="3" t="s">
+      <c r="G19" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H19" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="G19" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="H19" s="6" t="s">
+      <c r="I19" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="I19" s="6" t="s">
-        <v>77</v>
-      </c>
     </row>
     <row r="20" spans="2:9" ht="24" customHeight="1">
-      <c r="B20" s="25"/>
+      <c r="B20" s="22"/>
       <c r="C20" s="4">
         <v>12</v>
       </c>
       <c r="D20" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="E20" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="E20" s="3" t="s">
+      <c r="F20" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="F20" s="3" t="s">
+      <c r="G20" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H20" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="G20" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="H20" s="6" t="s">
+      <c r="I20" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="I20" s="6" t="s">
-        <v>82</v>
-      </c>
     </row>
     <row r="21" spans="2:9" ht="34.5" customHeight="1">
-      <c r="B21" s="25"/>
+      <c r="B21" s="22"/>
       <c r="C21" s="4">
         <v>13</v>
       </c>
       <c r="D21" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="E21" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="E21" s="3" t="s">
+      <c r="F21" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="F21" s="3" t="s">
+      <c r="G21" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H21" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="G21" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="H21" s="6" t="s">
+      <c r="I21" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="I21" s="6" t="s">
-        <v>87</v>
-      </c>
     </row>
     <row r="22" spans="2:9" ht="48" customHeight="1">
-      <c r="B22" s="26"/>
+      <c r="B22" s="23"/>
       <c r="C22" s="4">
         <v>14</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E22" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="F22" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="F22" s="3" t="s">
+      <c r="G22" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H22" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="G22" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="H22" s="6" t="s">
+      <c r="I22" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="I22" s="6" t="s">
+    </row>
+    <row r="23" spans="2:9" ht="34.5" customHeight="1">
+      <c r="B23" s="21" t="s">
         <v>91</v>
-      </c>
-    </row>
-    <row r="23" spans="2:9" ht="34.5" customHeight="1">
-      <c r="B23" s="24" t="s">
-        <v>92</v>
       </c>
       <c r="C23" s="4">
         <v>15</v>
       </c>
       <c r="D23" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="E23" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="E23" s="3" t="s">
+      <c r="F23" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="F23" s="3" t="s">
+      <c r="G23" s="5" t="s">
         <v>95</v>
-      </c>
-      <c r="G23" s="5" t="s">
-        <v>96</v>
       </c>
       <c r="H23" s="6"/>
       <c r="I23" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="24" spans="2:9" ht="34.5" customHeight="1">
-      <c r="B24" s="25"/>
+      <c r="B24" s="22"/>
       <c r="C24" s="4">
         <v>16</v>
       </c>
       <c r="D24" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="E24" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="E24" s="3" t="s">
+      <c r="F24" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="F24" s="3" t="s">
+      <c r="G24" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H24" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="G24" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="H24" s="6" t="s">
+      <c r="I24" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="I24" s="6" t="s">
-        <v>102</v>
-      </c>
     </row>
     <row r="25" spans="2:9" ht="61.5" customHeight="1">
-      <c r="B25" s="25"/>
+      <c r="B25" s="22"/>
       <c r="C25" s="4">
         <v>17</v>
       </c>
       <c r="D25" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="E25" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="E25" s="3" t="s">
+      <c r="F25" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="F25" s="3" t="s">
+      <c r="G25" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H25" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="G25" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="H25" s="6" t="s">
+      <c r="I25" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="I25" s="6" t="s">
-        <v>107</v>
-      </c>
     </row>
     <row r="26" spans="2:9" ht="24" customHeight="1">
-      <c r="B26" s="25"/>
+      <c r="B26" s="22"/>
       <c r="C26" s="4">
         <v>18</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E26" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="F26" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="F26" s="3" t="s">
+      <c r="G26" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H26" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="G26" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="H26" s="6" t="s">
+      <c r="I26" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="I26" s="6" t="s">
-        <v>111</v>
-      </c>
     </row>
     <row r="27" spans="2:9" ht="24" customHeight="1">
-      <c r="B27" s="26"/>
+      <c r="B27" s="23"/>
       <c r="C27" s="4">
         <v>19</v>
       </c>
       <c r="D27" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="E27" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="E27" s="3" t="s">
+      <c r="F27" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="F27" s="3" t="s">
+      <c r="G27" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H27" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="G27" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="H27" s="6" t="s">
+      <c r="I27" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="I27" s="6" t="s">
+    </row>
+    <row r="28" spans="2:9" ht="24" customHeight="1">
+      <c r="B28" s="21" t="s">
         <v>116</v>
-      </c>
-    </row>
-    <row r="28" spans="2:9" ht="24" customHeight="1">
-      <c r="B28" s="24" t="s">
-        <v>117</v>
       </c>
       <c r="C28" s="4">
         <v>20</v>
       </c>
       <c r="D28" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="E28" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="E28" s="3" t="s">
+      <c r="F28" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="F28" s="3" t="s">
+      <c r="G28" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H28" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="G28" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="H28" s="6" t="s">
+      <c r="I28" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="I28" s="6" t="s">
+    </row>
+    <row r="29" spans="2:9" ht="48" customHeight="1">
+      <c r="B29" s="22"/>
+      <c r="C29" s="4">
+        <v>21</v>
+      </c>
+      <c r="D29" s="4" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="29" spans="2:9" ht="48" customHeight="1">
-      <c r="B29" s="25"/>
-      <c r="C29" s="4">
-        <v>21</v>
-      </c>
-      <c r="D29" s="4" t="s">
+      <c r="E29" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="E29" s="3" t="s">
+      <c r="F29" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="F29" s="3" t="s">
+      <c r="G29" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H29" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="G29" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="H29" s="6" t="s">
+      <c r="I29" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="I29" s="6" t="s">
-        <v>127</v>
-      </c>
     </row>
     <row r="30" spans="2:9" ht="34.5" customHeight="1">
-      <c r="B30" s="25"/>
+      <c r="B30" s="22"/>
       <c r="C30" s="4">
         <v>22</v>
       </c>
       <c r="D30" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="E30" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="E30" s="3" t="s">
+      <c r="F30" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="F30" s="3" t="s">
+      <c r="G30" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H30" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="G30" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="H30" s="6" t="s">
+      <c r="I30" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="I30" s="6" t="s">
-        <v>132</v>
-      </c>
     </row>
     <row r="31" spans="2:9" ht="34.5" customHeight="1">
-      <c r="B31" s="25"/>
+      <c r="B31" s="22"/>
       <c r="C31" s="4">
         <v>23</v>
       </c>
       <c r="D31" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="E31" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="E31" s="3" t="s">
+      <c r="F31" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="F31" s="3" t="s">
+      <c r="G31" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H31" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="G31" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="H31" s="6" t="s">
+      <c r="I31" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="I31" s="6" t="s">
-        <v>137</v>
-      </c>
     </row>
     <row r="32" spans="2:9" ht="24" customHeight="1">
-      <c r="B32" s="26"/>
+      <c r="B32" s="23"/>
       <c r="C32" s="4">
         <v>24</v>
       </c>
       <c r="D32" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="E32" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="E32" s="3" t="s">
+      <c r="F32" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="F32" s="7" t="s">
+      <c r="G32" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H32" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="G32" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="H32" s="6" t="s">
+      <c r="I32" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="I32" s="6" t="s">
+    </row>
+    <row r="33" spans="2:9" ht="34.5" customHeight="1">
+      <c r="B33" s="21" t="s">
         <v>142</v>
-      </c>
-    </row>
-    <row r="33" spans="2:9" ht="34.5" customHeight="1">
-      <c r="B33" s="24" t="s">
-        <v>143</v>
       </c>
       <c r="C33" s="4">
         <v>25</v>
       </c>
       <c r="D33" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="E33" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="E33" s="3" t="s">
+      <c r="F33" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="F33" s="3" t="s">
+      <c r="G33" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H33" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="G33" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="H33" s="6" t="s">
+      <c r="I33" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="I33" s="6" t="s">
-        <v>148</v>
-      </c>
     </row>
     <row r="34" spans="2:9" ht="24" customHeight="1">
-      <c r="B34" s="25"/>
+      <c r="B34" s="22"/>
       <c r="C34" s="4">
         <v>26</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E34" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="F34" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="F34" s="3" t="s">
+      <c r="G34" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H34" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="G34" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="H34" s="6" t="s">
+      <c r="I34" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="I34" s="6" t="s">
-        <v>152</v>
-      </c>
     </row>
     <row r="35" spans="2:9" ht="48" customHeight="1">
-      <c r="B35" s="26"/>
+      <c r="B35" s="23"/>
       <c r="C35" s="4">
         <v>27</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G35" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H35" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="H35" s="6" t="s">
+      <c r="I35" s="6" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="37" spans="2:9" ht="19.5" customHeight="1">
+      <c r="B37" s="39" t="s">
         <v>155</v>
       </c>
-      <c r="I35" s="6" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="37" spans="2:9" ht="19.5" customHeight="1">
-      <c r="B37" s="38" t="s">
-        <v>157</v>
-      </c>
-      <c r="C37" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="D37" s="20"/>
-      <c r="E37" s="21"/>
+      <c r="C37" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="D37" s="19"/>
+      <c r="E37" s="20"/>
       <c r="F37" s="10">
         <f>COUNTIF($G$9:$G$35,"통과")</f>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G37" s="27" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="H37" s="28"/>
       <c r="I37" s="29"/>
     </row>
     <row r="38" spans="2:9" ht="19.5" customHeight="1">
-      <c r="B38" s="25"/>
-      <c r="C38" s="19" t="s">
-        <v>159</v>
-      </c>
-      <c r="D38" s="20"/>
-      <c r="E38" s="21"/>
+      <c r="B38" s="22"/>
+      <c r="C38" s="25" t="s">
+        <v>157</v>
+      </c>
+      <c r="D38" s="19"/>
+      <c r="E38" s="20"/>
       <c r="F38" s="10">
         <f>COUNTIF($G$9:$G$35,"실패")</f>
         <v>0</v>
       </c>
       <c r="G38" s="30"/>
-      <c r="H38" s="23"/>
-      <c r="I38" s="31"/>
+      <c r="H38" s="31"/>
+      <c r="I38" s="32"/>
     </row>
     <row r="39" spans="2:9" ht="19.5" customHeight="1">
-      <c r="B39" s="25"/>
-      <c r="C39" s="19" t="s">
-        <v>154</v>
-      </c>
-      <c r="D39" s="20"/>
-      <c r="E39" s="21"/>
+      <c r="B39" s="22"/>
+      <c r="C39" s="25" t="s">
+        <v>153</v>
+      </c>
+      <c r="D39" s="19"/>
+      <c r="E39" s="20"/>
       <c r="F39" s="10">
         <f>COUNTIF($G$9:$G$35,"미확인")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G39" s="30"/>
-      <c r="H39" s="23"/>
-      <c r="I39" s="31"/>
+      <c r="H39" s="31"/>
+      <c r="I39" s="32"/>
     </row>
     <row r="40" spans="2:9" ht="19.5" customHeight="1">
-      <c r="B40" s="25"/>
-      <c r="C40" s="19" t="s">
-        <v>96</v>
-      </c>
-      <c r="D40" s="20"/>
-      <c r="E40" s="21"/>
+      <c r="B40" s="22"/>
+      <c r="C40" s="25" t="s">
+        <v>95</v>
+      </c>
+      <c r="D40" s="19"/>
+      <c r="E40" s="20"/>
       <c r="F40" s="10">
         <f>COUNTIF($G$9:$G$35,"해당없음")</f>
         <v>1</v>
       </c>
       <c r="G40" s="30"/>
-      <c r="H40" s="23"/>
-      <c r="I40" s="31"/>
+      <c r="H40" s="31"/>
+      <c r="I40" s="32"/>
     </row>
     <row r="41" spans="2:9" ht="19.5" customHeight="1">
-      <c r="B41" s="25"/>
-      <c r="C41" s="19" t="s">
-        <v>160</v>
-      </c>
-      <c r="D41" s="20"/>
-      <c r="E41" s="21"/>
+      <c r="B41" s="22"/>
+      <c r="C41" s="25" t="s">
+        <v>158</v>
+      </c>
+      <c r="D41" s="19"/>
+      <c r="E41" s="20"/>
       <c r="F41" s="10">
         <f>COUNTA($E$9:$E$35)-COUNTA($G$9:$G$35)</f>
         <v>0</v>
       </c>
       <c r="G41" s="30"/>
-      <c r="H41" s="23"/>
-      <c r="I41" s="31"/>
+      <c r="H41" s="31"/>
+      <c r="I41" s="32"/>
     </row>
     <row r="42" spans="2:9" ht="19.5" customHeight="1">
-      <c r="B42" s="26"/>
-      <c r="C42" s="19" t="s">
-        <v>161</v>
-      </c>
-      <c r="D42" s="20"/>
-      <c r="E42" s="21"/>
+      <c r="B42" s="23"/>
+      <c r="C42" s="25" t="s">
+        <v>159</v>
+      </c>
+      <c r="D42" s="19"/>
+      <c r="E42" s="20"/>
       <c r="F42" s="10">
         <f>COUNTA($E$9:$E$35)</f>
         <v>27</v>
       </c>
-      <c r="G42" s="32"/>
-      <c r="H42" s="33"/>
-      <c r="I42" s="34"/>
+      <c r="G42" s="33"/>
+      <c r="H42" s="34"/>
+      <c r="I42" s="35"/>
     </row>
     <row r="43" spans="2:9" ht="7.5" customHeight="1"/>
     <row r="44" spans="2:9" ht="21.75" customHeight="1">
-      <c r="B44" s="40" t="s">
-        <v>162</v>
-      </c>
-      <c r="C44" s="20"/>
-      <c r="D44" s="20"/>
-      <c r="E44" s="20"/>
-      <c r="F44" s="20"/>
-      <c r="G44" s="20"/>
-      <c r="H44" s="20"/>
-      <c r="I44" s="21"/>
+      <c r="B44" s="24" t="s">
+        <v>160</v>
+      </c>
+      <c r="C44" s="19"/>
+      <c r="D44" s="19"/>
+      <c r="E44" s="19"/>
+      <c r="F44" s="19"/>
+      <c r="G44" s="19"/>
+      <c r="H44" s="19"/>
+      <c r="I44" s="20"/>
     </row>
     <row r="45" spans="2:9" ht="42" customHeight="1">
       <c r="B45" s="9" t="s">
-        <v>163</v>
-      </c>
-      <c r="C45" s="39"/>
-      <c r="D45" s="20"/>
-      <c r="E45" s="20"/>
-      <c r="F45" s="20"/>
-      <c r="G45" s="20"/>
-      <c r="H45" s="20"/>
-      <c r="I45" s="21"/>
+        <v>161</v>
+      </c>
+      <c r="C45" s="26" t="s">
+        <v>184</v>
+      </c>
+      <c r="D45" s="19"/>
+      <c r="E45" s="19"/>
+      <c r="F45" s="19"/>
+      <c r="G45" s="19"/>
+      <c r="H45" s="19"/>
+      <c r="I45" s="20"/>
     </row>
     <row r="46" spans="2:9" ht="42" customHeight="1">
       <c r="B46" s="9" t="s">
-        <v>164</v>
-      </c>
-      <c r="C46" s="39"/>
-      <c r="D46" s="20"/>
-      <c r="E46" s="20"/>
-      <c r="F46" s="20"/>
-      <c r="G46" s="20"/>
-      <c r="H46" s="20"/>
-      <c r="I46" s="21"/>
+        <v>162</v>
+      </c>
+      <c r="C46" s="26" t="s">
+        <v>185</v>
+      </c>
+      <c r="D46" s="19"/>
+      <c r="E46" s="19"/>
+      <c r="F46" s="19"/>
+      <c r="G46" s="19"/>
+      <c r="H46" s="19"/>
+      <c r="I46" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="C46:I46"/>
-    <mergeCell ref="B23:B27"/>
-    <mergeCell ref="C45:I45"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="B44:I44"/>
-    <mergeCell ref="C37:E37"/>
-    <mergeCell ref="C3:E3"/>
-    <mergeCell ref="B11:B13"/>
-    <mergeCell ref="C6:E6"/>
-    <mergeCell ref="C42:E42"/>
-    <mergeCell ref="B18:B22"/>
-    <mergeCell ref="C5:E5"/>
-    <mergeCell ref="G37:I42"/>
-    <mergeCell ref="C4:E4"/>
     <mergeCell ref="F3:I6"/>
     <mergeCell ref="B2:I2"/>
     <mergeCell ref="C39:E39"/>
@@ -2294,6 +2293,20 @@
     <mergeCell ref="B28:B32"/>
     <mergeCell ref="B33:B35"/>
     <mergeCell ref="B14:B17"/>
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="B11:B13"/>
+    <mergeCell ref="C6:E6"/>
+    <mergeCell ref="C42:E42"/>
+    <mergeCell ref="B18:B22"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="C4:E4"/>
+    <mergeCell ref="C46:I46"/>
+    <mergeCell ref="B23:B27"/>
+    <mergeCell ref="C45:I45"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="B44:I44"/>
+    <mergeCell ref="C37:E37"/>
+    <mergeCell ref="G37:I42"/>
   </mergeCells>
   <phoneticPr fontId="13" type="noConversion"/>
   <conditionalFormatting sqref="G9:G35">
@@ -2347,238 +2360,238 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="30" customHeight="1">
-      <c r="B2" s="45" t="s">
-        <v>165</v>
-      </c>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="23"/>
-      <c r="F2" s="23"/>
-      <c r="G2" s="23"/>
-      <c r="H2" s="23"/>
+      <c r="B2" s="41" t="s">
+        <v>163</v>
+      </c>
+      <c r="C2" s="31"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="31"/>
+      <c r="G2" s="31"/>
+      <c r="H2" s="31"/>
     </row>
     <row r="4" spans="2:8" ht="45.75" customHeight="1">
       <c r="B4" s="11" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C4" s="42" t="s">
-        <v>167</v>
-      </c>
-      <c r="D4" s="20"/>
-      <c r="E4" s="20"/>
-      <c r="F4" s="20"/>
-      <c r="G4" s="20"/>
-      <c r="H4" s="21"/>
+        <v>165</v>
+      </c>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
+      <c r="G4" s="19"/>
+      <c r="H4" s="20"/>
     </row>
     <row r="5" spans="2:8" ht="45.75" customHeight="1">
       <c r="B5" s="11" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C5" s="42" t="s">
-        <v>169</v>
-      </c>
-      <c r="D5" s="20"/>
-      <c r="E5" s="20"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="21"/>
+        <v>167</v>
+      </c>
+      <c r="D5" s="19"/>
+      <c r="E5" s="19"/>
+      <c r="F5" s="19"/>
+      <c r="G5" s="19"/>
+      <c r="H5" s="20"/>
     </row>
     <row r="6" spans="2:8" ht="81.75" customHeight="1">
       <c r="B6" s="11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C6" s="42" t="s">
-        <v>170</v>
-      </c>
-      <c r="D6" s="20"/>
-      <c r="E6" s="20"/>
-      <c r="F6" s="20"/>
-      <c r="G6" s="20"/>
-      <c r="H6" s="21"/>
+        <v>168</v>
+      </c>
+      <c r="D6" s="19"/>
+      <c r="E6" s="19"/>
+      <c r="F6" s="19"/>
+      <c r="G6" s="19"/>
+      <c r="H6" s="20"/>
     </row>
     <row r="7" spans="2:8" ht="45.75" customHeight="1">
       <c r="B7" s="11" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C7" s="42" t="s">
-        <v>172</v>
-      </c>
-      <c r="D7" s="20"/>
-      <c r="E7" s="20"/>
-      <c r="F7" s="20"/>
-      <c r="G7" s="20"/>
-      <c r="H7" s="21"/>
+        <v>170</v>
+      </c>
+      <c r="D7" s="19"/>
+      <c r="E7" s="19"/>
+      <c r="F7" s="19"/>
+      <c r="G7" s="19"/>
+      <c r="H7" s="20"/>
     </row>
     <row r="8" spans="2:8" ht="27.75" customHeight="1">
       <c r="B8" s="11" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C8" s="42" t="s">
-        <v>173</v>
-      </c>
-      <c r="D8" s="20"/>
-      <c r="E8" s="20"/>
-      <c r="F8" s="20"/>
-      <c r="G8" s="20"/>
-      <c r="H8" s="21"/>
+        <v>171</v>
+      </c>
+      <c r="D8" s="19"/>
+      <c r="E8" s="19"/>
+      <c r="F8" s="19"/>
+      <c r="G8" s="19"/>
+      <c r="H8" s="20"/>
     </row>
     <row r="9" spans="2:8" ht="45.75" customHeight="1">
       <c r="B9" s="11" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C9" s="42" t="s">
-        <v>175</v>
-      </c>
-      <c r="D9" s="20"/>
-      <c r="E9" s="20"/>
-      <c r="F9" s="20"/>
-      <c r="G9" s="20"/>
-      <c r="H9" s="21"/>
+        <v>173</v>
+      </c>
+      <c r="D9" s="19"/>
+      <c r="E9" s="19"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="19"/>
+      <c r="H9" s="20"/>
     </row>
     <row r="10" spans="2:8" ht="27.75" customHeight="1">
       <c r="B10" s="11" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C10" s="43" t="s">
-        <v>177</v>
-      </c>
-      <c r="D10" s="20"/>
-      <c r="E10" s="20"/>
-      <c r="F10" s="20"/>
-      <c r="G10" s="20"/>
-      <c r="H10" s="21"/>
+        <v>175</v>
+      </c>
+      <c r="D10" s="19"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="19"/>
+      <c r="H10" s="20"/>
     </row>
     <row r="12" spans="2:8" ht="15" customHeight="1">
       <c r="B12" s="44" t="s">
-        <v>178</v>
-      </c>
-      <c r="C12" s="23"/>
-      <c r="D12" s="23"/>
-      <c r="E12" s="23"/>
-      <c r="F12" s="23"/>
-      <c r="G12" s="23"/>
-      <c r="H12" s="23"/>
+        <v>176</v>
+      </c>
+      <c r="C12" s="31"/>
+      <c r="D12" s="31"/>
+      <c r="E12" s="31"/>
+      <c r="F12" s="31"/>
+      <c r="G12" s="31"/>
+      <c r="H12" s="31"/>
     </row>
     <row r="13" spans="2:8" ht="15" customHeight="1">
       <c r="B13" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="C13" s="12" t="s">
+      <c r="D13" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="D13" s="12" t="s">
+      <c r="E13" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="E13" s="12" t="s">
-        <v>13</v>
-      </c>
       <c r="F13" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="G13" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="G13" s="12" t="s">
+      <c r="H13" s="12" t="s">
         <v>16</v>
-      </c>
-      <c r="H13" s="12" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="14" spans="2:8" ht="45.75" customHeight="1">
       <c r="B14" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C14" s="13">
         <v>4</v>
       </c>
       <c r="D14" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E14" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>37</v>
-      </c>
       <c r="F14" s="15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G14" s="14" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="H14" s="3"/>
     </row>
     <row r="15" spans="2:8" ht="45.75" customHeight="1">
       <c r="B15" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C15" s="13">
         <v>9</v>
       </c>
       <c r="D15" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="E15" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="E15" s="3" t="s">
-        <v>63</v>
-      </c>
       <c r="F15" s="16" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="G15" s="14" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="16" spans="2:8" ht="45.75" customHeight="1">
       <c r="B16" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C16" s="13">
         <v>16</v>
       </c>
       <c r="D16" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="E16" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="E16" s="3" t="s">
-        <v>99</v>
-      </c>
       <c r="F16" s="17" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G16" s="3"/>
       <c r="H16" s="14" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="17" spans="2:8" ht="45.75" customHeight="1">
       <c r="B17" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C17" s="13">
         <v>20</v>
       </c>
       <c r="D17" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="E17" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="E17" s="3" t="s">
-        <v>119</v>
-      </c>
       <c r="F17" s="18" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G17" s="3"/>
       <c r="H17" s="14" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="C10:H10"/>
+    <mergeCell ref="C5:H5"/>
+    <mergeCell ref="C9:H9"/>
+    <mergeCell ref="B12:H12"/>
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="C8:H8"/>
     <mergeCell ref="C4:H4"/>
     <mergeCell ref="C7:H7"/>
     <mergeCell ref="C6:H6"/>
-    <mergeCell ref="C10:H10"/>
-    <mergeCell ref="C5:H5"/>
-    <mergeCell ref="C9:H9"/>
-    <mergeCell ref="B12:H12"/>
   </mergeCells>
   <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
